--- a/backtest_runs/20260410_193731/by_symbol/HMB/HMB.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/HMB/HMB.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>100000</v>
@@ -679,7 +679,7 @@
         <v>-6488.489999999997</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>93511.51000000001</v>
@@ -771,7 +771,7 @@
         <v>-403.769999999993</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>100140.85</v>
@@ -817,7 +817,7 @@
         <v>-75.1199999999984</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>100065.73</v>
@@ -909,7 +909,7 @@
         <v>-2478.96</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>97605.55</v>
@@ -955,7 +955,7 @@
         <v>-5371.079999999999</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>92234.47</v>
@@ -1093,7 +1093,7 @@
         <v>-441.3299999999989</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>92572.51000000001</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>95849.62</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>95849.62</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>95849.62</v>
@@ -1323,7 +1323,7 @@
         <v>-178.4099999999979</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>95671.21000000001</v>
@@ -1415,7 +1415,7 @@
         <v>-1577.519999999993</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>100610.35</v>
@@ -1461,7 +1461,7 @@
         <v>-56.34000000000214</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>100554.01</v>
@@ -1507,7 +1507,7 @@
         <v>-525.8400000000022</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>100028.17</v>
@@ -1645,7 +1645,7 @@
         <v>-2422.619999999999</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>106845.31</v>
